--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7400" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -216,13 +216,19 @@
     <t xml:space="preserve">it was a good day </t>
   </si>
   <si>
-    <t>Bad</t>
+    <t>Stressed</t>
   </si>
   <si>
     <t>Unsatisfied</t>
   </si>
   <si>
     <t>doesn't go well as i planned</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>need to work more on time management</t>
   </si>
 </sst>
 </file>
@@ -1949,7 +1955,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" ht="29" spans="1:14">
       <c r="A13" s="11">
         <v>46260</v>
       </c>
@@ -1959,30 +1965,46 @@
       <c r="C13" s="12">
         <v>45</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="D13" s="12">
+        <v>30</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
       <c r="F13" s="12">
         <v>350</v>
       </c>
       <c r="G13" s="12">
         <v>7</v>
       </c>
-      <c r="H13" s="12"/>
+      <c r="H13" s="12">
+        <v>0</v>
+      </c>
       <c r="I13" s="13">
         <f t="shared" si="0"/>
-        <v>815</v>
+        <v>845</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="1"/>
-        <v>625</v>
-      </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="15"/>
+        <v>595</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="11"/>
+      <c r="A14" s="11">
+        <v>46261</v>
+      </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -2004,7 +2026,9 @@
       <c r="N14" s="15"/>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="11"/>
+      <c r="A15" s="11">
+        <v>46262</v>
+      </c>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -2026,7 +2050,9 @@
       <c r="N15" s="15"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="11"/>
+      <c r="A16" s="11">
+        <v>46263</v>
+      </c>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
@@ -2048,7 +2074,9 @@
       <c r="N16" s="15"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="11"/>
+      <c r="A17" s="11">
+        <v>46264</v>
+      </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2070,7 +2098,9 @@
       <c r="N17" s="15"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="11"/>
+      <c r="A18" s="11">
+        <v>46265</v>
+      </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2092,7 +2122,9 @@
       <c r="N18" s="15"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="11"/>
+      <c r="A19" s="11">
+        <v>46266</v>
+      </c>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2114,7 +2146,9 @@
       <c r="N19" s="15"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="11"/>
+      <c r="A20" s="11">
+        <v>46267</v>
+      </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2136,7 +2170,9 @@
       <c r="N20" s="15"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="11"/>
+      <c r="A21" s="11">
+        <v>46268</v>
+      </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -2158,7 +2194,9 @@
       <c r="N21" s="15"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="11"/>
+      <c r="A22" s="11">
+        <v>46269</v>
+      </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -2180,7 +2218,9 @@
       <c r="N22" s="15"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="11"/>
+      <c r="A23" s="11">
+        <v>46270</v>
+      </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -2202,7 +2242,9 @@
       <c r="N23" s="15"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="11"/>
+      <c r="A24" s="11">
+        <v>46271</v>
+      </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -2224,7 +2266,9 @@
       <c r="N24" s="15"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="11"/>
+      <c r="A25" s="11">
+        <v>46272</v>
+      </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -2246,7 +2290,9 @@
       <c r="N25" s="15"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="11"/>
+      <c r="A26" s="11">
+        <v>46273</v>
+      </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -2268,7 +2314,9 @@
       <c r="N26" s="15"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="11"/>
+      <c r="A27" s="11">
+        <v>46274</v>
+      </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -2290,7 +2338,9 @@
       <c r="N27" s="15"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="11"/>
+      <c r="A28" s="11">
+        <v>46275</v>
+      </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
@@ -2312,7 +2362,9 @@
       <c r="N28" s="15"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="11"/>
+      <c r="A29" s="11">
+        <v>46276</v>
+      </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
@@ -2334,7 +2386,9 @@
       <c r="N29" s="15"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="11"/>
+      <c r="A30" s="11">
+        <v>46277</v>
+      </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -2356,7 +2410,9 @@
       <c r="N30" s="15"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="11"/>
+      <c r="A31" s="11">
+        <v>46278</v>
+      </c>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -2378,7 +2434,9 @@
       <c r="N31" s="15"/>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="11"/>
+      <c r="A32" s="11">
+        <v>46279</v>
+      </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -2400,7 +2458,9 @@
       <c r="N32" s="15"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="11"/>
+      <c r="A33" s="11">
+        <v>46280</v>
+      </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -2422,7 +2482,9 @@
       <c r="N33" s="15"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="11"/>
+      <c r="A34" s="11">
+        <v>46281</v>
+      </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
@@ -2444,7 +2506,9 @@
       <c r="N34" s="15"/>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="11"/>
+      <c r="A35" s="11">
+        <v>46282</v>
+      </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
@@ -2466,7 +2530,9 @@
       <c r="N35" s="15"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="11"/>
+      <c r="A36" s="11">
+        <v>46283</v>
+      </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -2488,7 +2554,9 @@
       <c r="N36" s="15"/>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="11"/>
+      <c r="A37" s="11">
+        <v>46284</v>
+      </c>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
@@ -2510,7 +2578,9 @@
       <c r="N37" s="15"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="11"/>
+      <c r="A38" s="11">
+        <v>46285</v>
+      </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
@@ -2532,7 +2602,9 @@
       <c r="N38" s="15"/>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="11"/>
+      <c r="A39" s="11">
+        <v>46286</v>
+      </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
@@ -2554,7 +2626,9 @@
       <c r="N39" s="15"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="11"/>
+      <c r="A40" s="11">
+        <v>46287</v>
+      </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
@@ -2576,7 +2650,9 @@
       <c r="N40" s="15"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="11"/>
+      <c r="A41" s="11">
+        <v>46288</v>
+      </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
@@ -2598,7 +2674,9 @@
       <c r="N41" s="15"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="11"/>
+      <c r="A42" s="11">
+        <v>46289</v>
+      </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7400" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -216,13 +216,25 @@
     <t xml:space="preserve">it was a good day </t>
   </si>
   <si>
-    <t>Bad</t>
+    <t>Stressed</t>
   </si>
   <si>
     <t>Unsatisfied</t>
   </si>
   <si>
     <t>doesn't go well as i planned</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>need to work more on time management</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>not satisfied completely</t>
   </si>
 </sst>
 </file>
@@ -1949,7 +1961,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" ht="29" spans="1:14">
       <c r="A13" s="11">
         <v>46260</v>
       </c>
@@ -1959,52 +1971,92 @@
       <c r="C13" s="12">
         <v>45</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="D13" s="12">
+        <v>30</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
       <c r="F13" s="12">
         <v>350</v>
       </c>
       <c r="G13" s="12">
         <v>7</v>
       </c>
-      <c r="H13" s="12"/>
+      <c r="H13" s="12">
+        <v>0</v>
+      </c>
       <c r="I13" s="13">
         <f t="shared" si="0"/>
-        <v>815</v>
+        <v>845</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="1"/>
-        <v>625</v>
-      </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="15"/>
+        <v>595</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="13" t="str">
+      <c r="A14" s="11">
+        <v>46261</v>
+      </c>
+      <c r="B14" s="12">
+        <v>375</v>
+      </c>
+      <c r="C14" s="12">
+        <v>45</v>
+      </c>
+      <c r="D14" s="12">
+        <v>240</v>
+      </c>
+      <c r="E14" s="12">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12">
+        <v>200</v>
+      </c>
+      <c r="G14" s="12">
+        <v>4</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="13" t="str">
+        <v>860</v>
+      </c>
+      <c r="J14" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="15"/>
+        <v>580</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="11"/>
+      <c r="A15" s="11">
+        <v>46262</v>
+      </c>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -2026,7 +2078,9 @@
       <c r="N15" s="15"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="11"/>
+      <c r="A16" s="11">
+        <v>46263</v>
+      </c>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
@@ -2048,7 +2102,9 @@
       <c r="N16" s="15"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="11"/>
+      <c r="A17" s="11">
+        <v>46264</v>
+      </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2070,7 +2126,9 @@
       <c r="N17" s="15"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="11"/>
+      <c r="A18" s="11">
+        <v>46265</v>
+      </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2092,7 +2150,9 @@
       <c r="N18" s="15"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="11"/>
+      <c r="A19" s="11">
+        <v>46266</v>
+      </c>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2114,7 +2174,9 @@
       <c r="N19" s="15"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="11"/>
+      <c r="A20" s="11">
+        <v>46267</v>
+      </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2136,7 +2198,9 @@
       <c r="N20" s="15"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="11"/>
+      <c r="A21" s="11">
+        <v>46268</v>
+      </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -2158,7 +2222,9 @@
       <c r="N21" s="15"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="11"/>
+      <c r="A22" s="11">
+        <v>46269</v>
+      </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -2180,7 +2246,9 @@
       <c r="N22" s="15"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="11"/>
+      <c r="A23" s="11">
+        <v>46270</v>
+      </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -2202,7 +2270,9 @@
       <c r="N23" s="15"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="11"/>
+      <c r="A24" s="11">
+        <v>46271</v>
+      </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -2224,7 +2294,9 @@
       <c r="N24" s="15"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="11"/>
+      <c r="A25" s="11">
+        <v>46272</v>
+      </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -2246,7 +2318,9 @@
       <c r="N25" s="15"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="11"/>
+      <c r="A26" s="11">
+        <v>46273</v>
+      </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -2268,7 +2342,9 @@
       <c r="N26" s="15"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="11"/>
+      <c r="A27" s="11">
+        <v>46274</v>
+      </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -2290,7 +2366,9 @@
       <c r="N27" s="15"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="11"/>
+      <c r="A28" s="11">
+        <v>46275</v>
+      </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
@@ -2312,7 +2390,9 @@
       <c r="N28" s="15"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="11"/>
+      <c r="A29" s="11">
+        <v>46276</v>
+      </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
@@ -2334,7 +2414,9 @@
       <c r="N29" s="15"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="11"/>
+      <c r="A30" s="11">
+        <v>46277</v>
+      </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -2356,7 +2438,9 @@
       <c r="N30" s="15"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="11"/>
+      <c r="A31" s="11">
+        <v>46278</v>
+      </c>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -2378,7 +2462,9 @@
       <c r="N31" s="15"/>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="11"/>
+      <c r="A32" s="11">
+        <v>46279</v>
+      </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -2400,7 +2486,9 @@
       <c r="N32" s="15"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="11"/>
+      <c r="A33" s="11">
+        <v>46280</v>
+      </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -2422,7 +2510,9 @@
       <c r="N33" s="15"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="11"/>
+      <c r="A34" s="11">
+        <v>46281</v>
+      </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
@@ -2444,7 +2534,9 @@
       <c r="N34" s="15"/>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="11"/>
+      <c r="A35" s="11">
+        <v>46282</v>
+      </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
@@ -2466,7 +2558,9 @@
       <c r="N35" s="15"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="11"/>
+      <c r="A36" s="11">
+        <v>46283</v>
+      </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -2488,7 +2582,9 @@
       <c r="N36" s="15"/>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="11"/>
+      <c r="A37" s="11">
+        <v>46284</v>
+      </c>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
@@ -2510,7 +2606,9 @@
       <c r="N37" s="15"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="11"/>
+      <c r="A38" s="11">
+        <v>46285</v>
+      </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
@@ -2532,7 +2630,9 @@
       <c r="N38" s="15"/>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="11"/>
+      <c r="A39" s="11">
+        <v>46286</v>
+      </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
@@ -2554,7 +2654,9 @@
       <c r="N39" s="15"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="11"/>
+      <c r="A40" s="11">
+        <v>46287</v>
+      </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
@@ -2576,7 +2678,9 @@
       <c r="N40" s="15"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="11"/>
+      <c r="A41" s="11">
+        <v>46288</v>
+      </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
@@ -2598,7 +2702,9 @@
       <c r="N41" s="15"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="11"/>
+      <c r="A42" s="11">
+        <v>46289</v>
+      </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7400" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,18 @@
   </si>
   <si>
     <t>need to work more on time management</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>not satisfied completely</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>feeling very low</t>
   </si>
 </sst>
 </file>
@@ -2005,49 +2017,93 @@
       <c r="A14" s="11">
         <v>46261</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="13" t="str">
+      <c r="B14" s="12">
+        <v>375</v>
+      </c>
+      <c r="C14" s="12">
+        <v>45</v>
+      </c>
+      <c r="D14" s="12">
+        <v>240</v>
+      </c>
+      <c r="E14" s="12">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12">
+        <v>200</v>
+      </c>
+      <c r="G14" s="12">
+        <v>4</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="13" t="str">
+        <v>860</v>
+      </c>
+      <c r="J14" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="15"/>
+        <v>580</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="11">
         <v>46262</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="13" t="str">
+      <c r="B15" s="12">
+        <v>240</v>
+      </c>
+      <c r="C15" s="12">
+        <v>0</v>
+      </c>
+      <c r="D15" s="12">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12">
+        <v>180</v>
+      </c>
+      <c r="G15" s="12">
+        <v>3</v>
+      </c>
+      <c r="H15" s="12">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="13" t="str">
+        <v>420</v>
+      </c>
+      <c r="J15" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="15"/>
+        <v>1020</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7400" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>feeling very low</t>
+  </si>
+  <si>
+    <t>felt better compared to other days</t>
   </si>
 </sst>
 </file>
@@ -2105,29 +2108,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" ht="29" spans="1:14">
       <c r="A16" s="11">
         <v>46263</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="13" t="str">
+      <c r="B16" s="12">
+        <v>780</v>
+      </c>
+      <c r="C16" s="12">
+        <v>0</v>
+      </c>
+      <c r="D16" s="12">
+        <v>150</v>
+      </c>
+      <c r="E16" s="12">
+        <v>180</v>
+      </c>
+      <c r="F16" s="12">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="13" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J16" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="15"/>
+        <v>330</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7400" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2154,29 +2154,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" ht="29" spans="1:14">
       <c r="A17" s="11">
         <v>46264</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="13" t="str">
+      <c r="B17" s="12">
+        <v>480</v>
+      </c>
+      <c r="C17" s="12">
+        <v>0</v>
+      </c>
+      <c r="D17" s="12">
+        <v>180</v>
+      </c>
+      <c r="E17" s="12">
+        <v>60</v>
+      </c>
+      <c r="F17" s="12">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0</v>
+      </c>
+      <c r="I17" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="13" t="str">
+        <v>720</v>
+      </c>
+      <c r="J17" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="15"/>
+        <v>720</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7400" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2204,25 +2204,47 @@
       <c r="A18" s="11">
         <v>46265</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="13" t="str">
+      <c r="B18" s="12">
+        <v>450</v>
+      </c>
+      <c r="C18" s="12">
+        <v>50</v>
+      </c>
+      <c r="D18" s="12">
+        <v>60</v>
+      </c>
+      <c r="E18" s="12">
+        <v>0</v>
+      </c>
+      <c r="F18" s="12">
+        <v>200</v>
+      </c>
+      <c r="G18" s="12">
+        <v>4</v>
+      </c>
+      <c r="H18" s="12">
+        <v>30</v>
+      </c>
+      <c r="I18" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="13" t="str">
+        <v>790</v>
+      </c>
+      <c r="J18" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="15"/>
+        <v>650</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7400" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>felt better compared to other days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">felt vey low </t>
   </si>
 </sst>
 </file>
@@ -2250,25 +2253,47 @@
       <c r="A19" s="11">
         <v>46266</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="13" t="str">
+      <c r="B19" s="12">
+        <v>450</v>
+      </c>
+      <c r="C19" s="12">
+        <v>45</v>
+      </c>
+      <c r="D19" s="12">
+        <v>0</v>
+      </c>
+      <c r="E19" s="12">
+        <v>0</v>
+      </c>
+      <c r="F19" s="12">
+        <v>350</v>
+      </c>
+      <c r="G19" s="12">
+        <v>7</v>
+      </c>
+      <c r="H19" s="12">
+        <v>0</v>
+      </c>
+      <c r="I19" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="13" t="str">
+        <v>845</v>
+      </c>
+      <c r="J19" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="15"/>
+        <v>595</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N19" s="15" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7400" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t xml:space="preserve">felt vey low </t>
+  </si>
+  <si>
+    <t>felt very low</t>
   </si>
 </sst>
 </file>
@@ -2299,25 +2302,47 @@
       <c r="A20" s="11">
         <v>46267</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="13" t="str">
+      <c r="B20" s="12">
+        <v>430</v>
+      </c>
+      <c r="C20" s="12">
+        <v>45</v>
+      </c>
+      <c r="D20" s="12">
+        <v>60</v>
+      </c>
+      <c r="E20" s="12">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12">
+        <v>350</v>
+      </c>
+      <c r="G20" s="12">
+        <v>7</v>
+      </c>
+      <c r="H20" s="12">
+        <v>30</v>
+      </c>
+      <c r="I20" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="13" t="str">
+        <v>915</v>
+      </c>
+      <c r="J20" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="15"/>
+        <v>525</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N20" s="15" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>felt very low</t>
+  </si>
+  <si>
+    <t>felt neutral</t>
   </si>
 </sst>
 </file>
@@ -2348,25 +2351,47 @@
       <c r="A21" s="11">
         <v>46268</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="13" t="str">
+      <c r="B21" s="12">
+        <v>420</v>
+      </c>
+      <c r="C21" s="12">
+        <v>0</v>
+      </c>
+      <c r="D21" s="12">
+        <v>120</v>
+      </c>
+      <c r="E21" s="12">
+        <v>80</v>
+      </c>
+      <c r="F21" s="12">
+        <v>200</v>
+      </c>
+      <c r="G21" s="12">
+        <v>3</v>
+      </c>
+      <c r="H21" s="12">
+        <v>0</v>
+      </c>
+      <c r="I21" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="13" t="str">
+        <v>820</v>
+      </c>
+      <c r="J21" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="15"/>
+        <v>620</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" s="15" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>felt neutral</t>
+  </si>
+  <si>
+    <t>felt a bit tired</t>
   </si>
 </sst>
 </file>
@@ -2397,25 +2400,47 @@
       <c r="A22" s="11">
         <v>46269</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="13" t="str">
+      <c r="B22" s="12">
+        <v>420</v>
+      </c>
+      <c r="C22" s="12">
+        <v>45</v>
+      </c>
+      <c r="D22" s="12">
+        <v>120</v>
+      </c>
+      <c r="E22" s="12">
+        <v>0</v>
+      </c>
+      <c r="F22" s="12">
+        <v>300</v>
+      </c>
+      <c r="G22" s="12">
+        <v>6</v>
+      </c>
+      <c r="H22" s="12">
+        <v>30</v>
+      </c>
+      <c r="I22" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="13" t="str">
+        <v>915</v>
+      </c>
+      <c r="J22" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="15"/>
+        <v>525</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" s="15" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>felt a bit tired</t>
+  </si>
+  <si>
+    <t>felt good</t>
   </si>
 </sst>
 </file>
@@ -2446,25 +2449,47 @@
       <c r="A23" s="11">
         <v>46270</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="13" t="str">
+      <c r="B23" s="12">
+        <v>360</v>
+      </c>
+      <c r="C23" s="12">
+        <v>45</v>
+      </c>
+      <c r="D23" s="12">
+        <v>240</v>
+      </c>
+      <c r="E23" s="12">
+        <v>80</v>
+      </c>
+      <c r="F23" s="12">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12">
+        <v>0</v>
+      </c>
+      <c r="I23" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="13" t="str">
+        <v>725</v>
+      </c>
+      <c r="J23" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="15"/>
+        <v>715</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N23" s="15" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7400" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>felt good</t>
+  </si>
+  <si>
+    <t>it was a neutral day</t>
   </si>
 </sst>
 </file>
@@ -2495,25 +2498,47 @@
       <c r="A24" s="11">
         <v>46271</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="13" t="str">
+      <c r="B24" s="12">
+        <v>430</v>
+      </c>
+      <c r="C24" s="12">
+        <v>45</v>
+      </c>
+      <c r="D24" s="12">
+        <v>240</v>
+      </c>
+      <c r="E24" s="12">
+        <v>0</v>
+      </c>
+      <c r="F24" s="12">
+        <v>0</v>
+      </c>
+      <c r="G24" s="12">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12">
+        <v>0</v>
+      </c>
+      <c r="I24" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="13" t="str">
+        <v>715</v>
+      </c>
+      <c r="J24" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="15"/>
+        <v>725</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N24" s="15" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>it was a neutral day</t>
+  </si>
+  <si>
+    <t>felt low</t>
   </si>
 </sst>
 </file>
@@ -2544,25 +2547,47 @@
       <c r="A25" s="11">
         <v>46272</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="13" t="str">
+      <c r="B25" s="12">
+        <v>370</v>
+      </c>
+      <c r="C25" s="12">
+        <v>45</v>
+      </c>
+      <c r="D25" s="12">
+        <v>180</v>
+      </c>
+      <c r="E25" s="12">
+        <v>0</v>
+      </c>
+      <c r="F25" s="12">
+        <v>180</v>
+      </c>
+      <c r="G25" s="12">
+        <v>3</v>
+      </c>
+      <c r="H25" s="12">
+        <v>0</v>
+      </c>
+      <c r="I25" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="13" t="str">
+        <v>775</v>
+      </c>
+      <c r="J25" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="15"/>
+        <v>665</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N25" s="15" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7400" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2593,25 +2593,47 @@
       <c r="A26" s="11">
         <v>46273</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="13" t="str">
+      <c r="B26" s="12">
+        <v>390</v>
+      </c>
+      <c r="C26" s="12">
+        <v>0</v>
+      </c>
+      <c r="D26" s="12">
+        <v>120</v>
+      </c>
+      <c r="E26" s="12">
+        <v>0</v>
+      </c>
+      <c r="F26" s="12">
+        <v>420</v>
+      </c>
+      <c r="G26" s="12">
+        <v>7</v>
+      </c>
+      <c r="H26" s="12">
+        <v>0</v>
+      </c>
+      <c r="I26" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="13" t="str">
+        <v>930</v>
+      </c>
+      <c r="J26" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="15"/>
+        <v>510</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N26" s="15" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2639,25 +2639,47 @@
       <c r="A27" s="11">
         <v>46274</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="13" t="str">
+      <c r="B27" s="12">
+        <v>410</v>
+      </c>
+      <c r="C27" s="12">
+        <v>45</v>
+      </c>
+      <c r="D27" s="12">
+        <v>120</v>
+      </c>
+      <c r="E27" s="12">
+        <v>60</v>
+      </c>
+      <c r="F27" s="12">
+        <v>420</v>
+      </c>
+      <c r="G27" s="12">
+        <v>5</v>
+      </c>
+      <c r="H27" s="12">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="13" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J27" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="15"/>
+        <v>385</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N27" s="15" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="11">

--- a/12627505.xlsx
+++ b/12627505.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7400" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2685,25 +2685,47 @@
       <c r="A28" s="11">
         <v>46275</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="13" t="str">
+      <c r="B28" s="12">
+        <v>480</v>
+      </c>
+      <c r="C28" s="12">
+        <v>0</v>
+      </c>
+      <c r="D28" s="12">
+        <v>120</v>
+      </c>
+      <c r="E28" s="12">
+        <v>120</v>
+      </c>
+      <c r="F28" s="12">
+        <v>240</v>
+      </c>
+      <c r="G28" s="12">
+        <v>3</v>
+      </c>
+      <c r="H28" s="12">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="13" t="str">
+        <v>960</v>
+      </c>
+      <c r="J28" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="15"/>
+        <v>480</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N28" s="15" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="11">
